--- a/Base/Backlog_36.xlsx
+++ b/Base/Backlog_36.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EEB558-74FB-4E8A-81CC-D341C6041C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35B055D-2C3E-4491-BC0C-2FA19D74290D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -205,9 +205,6 @@
     <t>INC-1554</t>
   </si>
   <si>
-    <t>Sostenes Silva</t>
-  </si>
-  <si>
     <t>Lourival Silva</t>
   </si>
   <si>
@@ -254,6 +251,9 @@
   </si>
   <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Sostenes Simões</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C2" s="11">
         <v>2025</v>
@@ -796,8 +796,8 @@
       <c r="F2" s="12">
         <v>45912</v>
       </c>
-      <c r="G2" s="11">
-        <v>344208</v>
+      <c r="G2" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="H2" s="13">
         <v>45870</v>
@@ -817,7 +817,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" s="11">
         <v>2025</v>
@@ -831,11 +831,11 @@
       <c r="F3" s="12">
         <v>45912</v>
       </c>
-      <c r="G3" s="11">
-        <v>344387</v>
+      <c r="G3" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="H3" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I3" s="12">
         <v>45908</v>
@@ -852,7 +852,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C4" s="11">
         <v>2025</v>
@@ -866,11 +866,11 @@
       <c r="F4" s="12">
         <v>45912</v>
       </c>
-      <c r="G4" s="11">
-        <v>344437</v>
+      <c r="G4" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="H4" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I4" s="12">
         <v>45908</v>
@@ -887,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C5" s="11">
         <v>2025</v>
@@ -901,8 +901,8 @@
       <c r="F5" s="12">
         <v>45912</v>
       </c>
-      <c r="G5" s="11">
-        <v>344693</v>
+      <c r="G5" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="H5" s="13">
         <v>45870</v>
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C6" s="11">
         <v>2025</v>
@@ -936,17 +936,17 @@
       <c r="F6" s="12">
         <v>45912</v>
       </c>
-      <c r="G6" s="11">
-        <v>344735</v>
+      <c r="G6" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="H6" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I6" s="12">
         <v>45908</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>11</v>
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="11">
         <v>2025</v>
@@ -972,16 +972,16 @@
         <v>45912</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H7" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I7" s="12">
         <v>45908</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>11</v>
@@ -992,7 +992,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="11">
         <v>2025</v>
@@ -1007,7 +1007,7 @@
         <v>45912</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="H8" s="13">
         <v>45901</v>
@@ -1016,7 +1016,7 @@
         <v>45908</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>11</v>
@@ -1027,7 +1027,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" s="11">
         <v>2025</v>
@@ -1042,10 +1042,10 @@
         <v>45912</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H9" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I9" s="12">
         <v>45908</v>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C10" s="11">
         <v>2025</v>
@@ -1077,16 +1077,16 @@
         <v>45912</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H10" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I10" s="12">
         <v>45908</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>11</v>
@@ -1097,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11">
         <v>2025</v>
@@ -1111,8 +1111,8 @@
       <c r="F11" s="12">
         <v>45912</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>28</v>
+      <c r="G11" s="11">
+        <v>344208</v>
       </c>
       <c r="H11" s="13">
         <v>45870</v>
@@ -1146,8 +1146,8 @@
       <c r="F12" s="12">
         <v>45912</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>29</v>
+      <c r="G12" s="11">
+        <v>344735</v>
       </c>
       <c r="H12" s="13">
         <v>45870</v>
@@ -1156,7 +1156,7 @@
         <v>45908</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>11</v>
@@ -1167,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C13" s="11">
         <v>2025</v>
@@ -1182,16 +1182,16 @@
         <v>45912</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I13" s="12">
         <v>45908</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>11</v>
@@ -1202,7 +1202,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C14" s="11">
         <v>2025</v>
@@ -1217,16 +1217,16 @@
         <v>45912</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H14" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I14" s="12">
         <v>45908</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>11</v>
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C15" s="11">
         <v>2025</v>
@@ -1252,16 +1252,16 @@
         <v>45912</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H15" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I15" s="12">
         <v>45908</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>11</v>
@@ -1287,16 +1287,16 @@
         <v>45912</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H16" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I16" s="12">
         <v>45908</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>11</v>
@@ -1307,7 +1307,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C17" s="11">
         <v>2025</v>
@@ -1322,10 +1322,10 @@
         <v>45912</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H17" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I17" s="12">
         <v>45908</v>
@@ -1342,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" s="11">
         <v>2025</v>
@@ -1357,7 +1357,7 @@
         <v>45912</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H18" s="13">
         <v>45901</v>
@@ -1377,7 +1377,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C19" s="11">
         <v>2025</v>
@@ -1392,7 +1392,7 @@
         <v>45912</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H19" s="13">
         <v>45901</v>
@@ -1412,7 +1412,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C20" s="11">
         <v>2025</v>
@@ -1426,17 +1426,17 @@
       <c r="F20" s="12">
         <v>45912</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>37</v>
+      <c r="G20" s="11">
+        <v>344693</v>
       </c>
       <c r="H20" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I20" s="12">
         <v>45908</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>11</v>
@@ -1447,7 +1447,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C21" s="11">
         <v>2025</v>
@@ -1462,10 +1462,10 @@
         <v>45912</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H21" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I21" s="12">
         <v>45908</v>
@@ -1482,7 +1482,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C22" s="11">
         <v>2025</v>
@@ -1497,7 +1497,7 @@
         <v>45912</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H22" s="13">
         <v>45901</v>
@@ -1517,7 +1517,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C23" s="11">
         <v>2025</v>
@@ -1532,16 +1532,16 @@
         <v>45912</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H23" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I23" s="12">
         <v>45908</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>11</v>
@@ -1552,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24" s="11">
         <v>2025</v>
@@ -1566,17 +1566,17 @@
       <c r="F24" s="12">
         <v>45912</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>41</v>
+      <c r="G24" s="11">
+        <v>344437</v>
       </c>
       <c r="H24" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I24" s="12">
         <v>45908</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>11</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C25" s="11">
         <v>2025</v>
@@ -1601,11 +1601,11 @@
       <c r="F25" s="12">
         <v>45912</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>42</v>
+      <c r="G25" s="11">
+        <v>344387</v>
       </c>
       <c r="H25" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I25" s="12">
         <v>45908</v>
@@ -1622,7 +1622,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="11">
         <v>2025</v>
@@ -1657,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="11">
         <v>2025</v>
@@ -1672,7 +1672,7 @@
         <v>45912</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H27" s="13">
         <v>45901</v>
@@ -1692,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C28" s="11">
         <v>2025</v>
@@ -1707,16 +1707,16 @@
         <v>45912</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H28" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I28" s="12">
         <v>45908</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>11</v>
@@ -1727,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C29" s="11">
         <v>2025</v>
@@ -1742,10 +1742,10 @@
         <v>45912</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H29" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I29" s="12">
         <v>45908</v>
@@ -1762,7 +1762,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="11">
         <v>2025</v>
@@ -1777,16 +1777,16 @@
         <v>45912</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H30" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I30" s="12">
         <v>45908</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>11</v>
@@ -1797,7 +1797,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="C31" s="11">
         <v>2025</v>
@@ -1812,7 +1812,7 @@
         <v>45912</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H31" s="13">
         <v>45870</v>
@@ -1832,7 +1832,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C32" s="11">
         <v>2025</v>
@@ -1847,10 +1847,10 @@
         <v>45912</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H32" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I32" s="12">
         <v>45908</v>
@@ -1867,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C33" s="11">
         <v>2025</v>
@@ -1882,16 +1882,16 @@
         <v>45912</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H33" s="13">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I33" s="12">
         <v>45908</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>11</v>
@@ -1902,7 +1902,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C34" s="11">
         <v>2025</v>
@@ -1917,10 +1917,10 @@
         <v>45912</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H34" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I34" s="12">
         <v>45908</v>
@@ -1937,7 +1937,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C35" s="11">
         <v>2025</v>
@@ -1952,7 +1952,7 @@
         <v>45912</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H35" s="13">
         <v>45901</v>
@@ -1961,7 +1961,7 @@
         <v>45908</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>11</v>
@@ -1972,7 +1972,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="C36" s="11">
         <v>2025</v>
@@ -1987,7 +1987,7 @@
         <v>45912</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H36" s="13">
         <v>45901</v>
@@ -2007,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="C37" s="11">
         <v>2025</v>
@@ -2022,10 +2022,10 @@
         <v>45912</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H37" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I37" s="12">
         <v>45908</v>
@@ -2042,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C38" s="11">
         <v>2025</v>
@@ -2057,16 +2057,16 @@
         <v>45912</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H38" s="13">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I38" s="12">
         <v>45908</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>11</v>
@@ -2123,7 +2123,11 @@
       <c r="I50" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K35" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
+  <autoFilter ref="A1:K35" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K38">
+      <sortCondition ref="B1:B35"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2189,7 +2193,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" s="11">
         <v>2025</v>
@@ -2213,7 +2217,7 @@
         <v>45908</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>15</v>
@@ -2224,7 +2228,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="14">
         <v>2025</v>
@@ -2239,7 +2243,7 @@
         <v>45912</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H3" s="15">
         <v>45901</v>
@@ -2248,7 +2252,7 @@
         <v>45908</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K3" s="14" t="s">
         <v>15</v>
@@ -2274,7 +2278,7 @@
         <v>45912</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H4" s="15">
         <v>45901</v>
@@ -2283,7 +2287,7 @@
         <v>45908</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>15</v>
@@ -2309,7 +2313,7 @@
         <v>45912</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H5" s="15">
         <v>45901</v>
@@ -2344,7 +2348,7 @@
         <v>45912</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H6" s="15">
         <v>45901</v>
@@ -2379,7 +2383,7 @@
         <v>45912</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H7" s="15">
         <v>45901</v>
@@ -2414,7 +2418,7 @@
         <v>45912</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" s="15">
         <v>45870</v>
@@ -2423,7 +2427,7 @@
         <v>45908</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>15</v>
@@ -2434,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="14">
         <v>2025</v>
@@ -2449,7 +2453,7 @@
         <v>45912</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H9" s="15">
         <v>45870</v>
@@ -2458,7 +2462,7 @@
         <v>45908</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>15</v>

--- a/Base/Backlog_36.xlsx
+++ b/Base/Backlog_36.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35B055D-2C3E-4491-BC0C-2FA19D74290D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EF4781-A2C2-4392-9C6D-16574A42BFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -208,15 +208,9 @@
     <t>Lourival Silva</t>
   </si>
   <si>
-    <t>Erick Silva</t>
-  </si>
-  <si>
     <t>Alana Oliveira</t>
   </si>
   <si>
-    <t>Higor Jesus</t>
-  </si>
-  <si>
     <t>Edson Junior</t>
   </si>
   <si>
@@ -254,6 +248,12 @@
   </si>
   <si>
     <t>Sostenes Simões</t>
+  </si>
+  <si>
+    <t>Erick da Silva</t>
+  </si>
+  <si>
+    <t>Higor Cruz</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="11">
         <v>2025</v>
@@ -817,7 +817,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="11">
         <v>2025</v>
@@ -852,7 +852,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="11">
         <v>2025</v>
@@ -887,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5" s="11">
         <v>2025</v>
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C6" s="11">
         <v>2025</v>
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C7" s="11">
         <v>2025</v>
@@ -981,7 +981,7 @@
         <v>45908</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>11</v>
@@ -992,7 +992,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C8" s="11">
         <v>2025</v>
@@ -1016,7 +1016,7 @@
         <v>45908</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>11</v>
@@ -1027,7 +1027,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="11">
         <v>2025</v>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C10" s="11">
         <v>2025</v>
@@ -1086,7 +1086,7 @@
         <v>45908</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>11</v>
@@ -1156,7 +1156,7 @@
         <v>45908</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>11</v>
@@ -1191,7 +1191,7 @@
         <v>45908</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>11</v>
@@ -1226,7 +1226,7 @@
         <v>45908</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>11</v>
@@ -1261,7 +1261,7 @@
         <v>45908</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>11</v>
@@ -1296,7 +1296,7 @@
         <v>45908</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>11</v>
@@ -1541,7 +1541,7 @@
         <v>45908</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>11</v>
@@ -1552,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C24" s="11">
         <v>2025</v>
@@ -1797,7 +1797,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="11">
         <v>2025</v>
@@ -1832,7 +1832,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C32" s="11">
         <v>2025</v>
@@ -1867,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" s="11">
         <v>2025</v>
@@ -1902,7 +1902,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" s="11">
         <v>2025</v>
@@ -1937,7 +1937,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" s="11">
         <v>2025</v>
@@ -1961,7 +1961,7 @@
         <v>45908</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>11</v>
@@ -1972,7 +1972,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" s="11">
         <v>2025</v>
@@ -2007,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" s="11">
         <v>2025</v>
@@ -2042,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C38" s="11">
         <v>2025</v>
@@ -2193,7 +2193,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C2" s="11">
         <v>2025</v>
@@ -2217,7 +2217,7 @@
         <v>45908</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>15</v>
@@ -2228,7 +2228,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C3" s="14">
         <v>2025</v>
@@ -2243,7 +2243,7 @@
         <v>45912</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H3" s="15">
         <v>45901</v>
@@ -2252,7 +2252,7 @@
         <v>45908</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K3" s="14" t="s">
         <v>15</v>
@@ -2278,7 +2278,7 @@
         <v>45912</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H4" s="15">
         <v>45901</v>
@@ -2287,7 +2287,7 @@
         <v>45908</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>15</v>
@@ -2313,7 +2313,7 @@
         <v>45912</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H5" s="15">
         <v>45901</v>
@@ -2348,7 +2348,7 @@
         <v>45912</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H6" s="15">
         <v>45901</v>
@@ -2383,7 +2383,7 @@
         <v>45912</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H7" s="15">
         <v>45901</v>
@@ -2418,7 +2418,7 @@
         <v>45912</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H8" s="15">
         <v>45870</v>
@@ -2427,7 +2427,7 @@
         <v>45908</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>15</v>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C9" s="14">
         <v>2025</v>
@@ -2453,7 +2453,7 @@
         <v>45912</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H9" s="15">
         <v>45870</v>
@@ -2462,7 +2462,7 @@
         <v>45908</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>15</v>
